--- a/interview_coding_NPL_1.xlsx
+++ b/interview_coding_NPL_1.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Interview Coding" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Wide Format" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Codebook Reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Stakeholder Analysis" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Interview: NPL_1  |  Country: NEPAL  |  Actor: Environmental Department  |  Source: Interview Guideline — Environmental Department (June 2023)</t>
+          <t>Interview: NPL_1  |  Country: NEPAL  |  Actor: Federal governmental (Department of Environment / Ministry)  |  Source: Interview Guideline — Environmental Department (June 2023)</t>
         </is>
       </c>
     </row>
@@ -637,7 +638,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Environmental Department / Ministry of Forests and Environment respondent.</t>
+          <t>Federal governmental actor (Department of Environment). Uses first-person 'we' for policy implementation, ministry-only questions (4.a/4.b), and describes Chief Secretary committee oversight.</t>
         </is>
       </c>
     </row>
@@ -671,7 +672,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -679,7 +680,11 @@
           <t>high, medium, low, NA — lack of awareness among policy makers mentioned</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Low political priority among decision-makers: 'no political will', plastics/waste 'not a priority' and 'stops at major' level.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -721,7 +726,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Blocking sewer systems; leakage into waterways.</t>
+          <t>Blocking sewer systems; leakage into waterways; landfill pressure.</t>
         </is>
       </c>
     </row>
@@ -765,7 +770,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Inadequate waste management; recycling participation via MRFs discussed.</t>
+          <t>Inadequate waste management; limited economically viable recycling for single-use items.</t>
         </is>
       </c>
     </row>
@@ -861,7 +866,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -869,7 +874,11 @@
           <t>Plastic imports are a problem; was mentioned: yes/no</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Import is part of the problem space: ban on production, import, and use of bags under 40 microns explicitly targets imported plastics.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -889,7 +898,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Waterways, urban systems, forests, health (burning/indoor), agriculture gaps in Chitwan.</t>
+          <t>Water (rivers/lakes), cities (sewers/urban), biodiversity (forests), health (burning/indoor air), agriculture (research gap noted for Chitwan).</t>
         </is>
       </c>
     </row>
@@ -969,7 +978,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Multi-level governance (national, district, municipal) with implementation gaps.</t>
+          <t>Challenges differ across national, district, and municipal levels; SWM Act revision needed for federal governance alignment.</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1036,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Department of Environment, Chief Secretary committee, Commerce and Supplies.</t>
+          <t>Department of Environment, Chief Secretary committee, Department of Commerce and Supplies.</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1076,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Local governments lead waste management.</t>
+          <t>Local governments lead waste management and collection.</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1160,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Not much research on plastic effects; more research needed.</t>
+          <t>Cites studies on microplastics; notes limited research on health/environmental effects.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1182,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Household waste collection with 300 NPR/month incentive for reduction.</t>
+          <t>Household waste reduction discussed; 300 NPR/month collector incentive mentioned (household incentive, not a product tax).</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1222,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Private contractors and market monitoring.</t>
+          <t>Private contractors, plastic producers, and markets monitored by Department of Environment.</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1284,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Funds exist but are not released; earmarked funds may be frozen.</t>
+          <t>Funds exist but are not released; earmarked funds may be frozen if unused.</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1326,11 @@
           <t>Lack of infrastructure</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Facilities exist in at least some contexts ('facility is there'); not coded as a primary lack-of-infrastructure barrier.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1417,7 +1430,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Documentaries, traditional/social media, website materials.</t>
+          <t>Government documentaries, traditional/social media, website materials.</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1496,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1493,7 +1506,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>300 NPR/month incentive for households reducing waste.</t>
+          <t>No levy/tax on specific products coded. The 300 NPR/month measure is a household waste-reduction incentive for collectors, not a bag tax/levy.</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1550,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Biodegradable starch bags discussed as existing alternative.</t>
+          <t>Biodegradable starch bags discussed as existing but costly alternative.</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1608,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Material recovery facilities and recycling to processing units.</t>
+          <t>Material recovery facilities send recyclables to processing units.</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1668,11 @@
           <t>Procedural measures to establish lead agency</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>High-level committee chaired by Chief Secretary oversees measures.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -1673,7 +1690,11 @@
           <t>Clear responsibilities</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>EPR framed as key missing responsibility mechanism.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -1727,7 +1748,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -1735,7 +1756,11 @@
           <t>Segregation of waste</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Collection/recycling encouraged, but segregation not proposed as a forward solution.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -1839,7 +1864,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -1857,7 +1882,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1865,7 +1890,11 @@
           <t>Ban of products</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Bans described as existing policy; forward-looking solutions emphasize EPR, R&amp;D, communication, and mitigation/adaptation rather than new bans.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -1885,7 +1914,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Financial support identified in Q10 follow-up.</t>
+          <t>Financial support identified in Q10.</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1936,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Infrastructural support identified in Q10 follow-up.</t>
+          <t>Infrastructural support identified in Q10.</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2042,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Follow-up asked but no specific tradition recorded in transcript.</t>
+          <t>Follow-up asked (Q8) but no specific tradition recorded.</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2528,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -2544,7 +2573,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -2699,7 +2728,7 @@
       </c>
       <c r="AT2" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AU2" s="7" t="inlineStr">
@@ -2759,7 +2788,7 @@
       </c>
       <c r="BF2" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="BG2" s="7" t="inlineStr">
@@ -2789,12 +2818,12 @@
       </c>
       <c r="BL2" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="BM2" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="BN2" s="7" t="inlineStr">
@@ -3728,4 +3757,128 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Stakeholder Analysis — NPL_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Interview ID</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>NPL_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>NEPAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Coded actor type</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>governmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Likely affiliation</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Department of Environment / Ministry of Forests and Environment (federal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Role in plastic governance</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>National policy design, monitoring of producers/markets, awareness campaigns, SWM Act revision</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Perspective</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Insider — describes measures as 'we' (government actor implementing national plastic policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>High for governmental coding; see RSCT note below</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>RSCT note</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Page 1 contains RSCT cooperative profile notes (est. 1991, 200+ cooperatives, grassroots loans, recently urban plastics). This does not match the interview voice in Themes A–D, which is clearly a federal ministry/department official. RSCT notes are treated as misplaced interviewer notes, not the coded stakeholder.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/interview_coding_NPL_1.xlsx
+++ b/interview_coding_NPL_1.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Wide Format" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Codebook Reference" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Stakeholder Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sources" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Interview: NPL_1  |  Country: NEPAL  |  Actor: Federal governmental (Department of Environment / Ministry)  |  Source: Interview Guideline — Environmental Department (June 2023)</t>
+          <t>Interview: NPL_1 (no. 5)  |  Country: NEPAL  |  Department of Environment — Deepak Diwali, Deputy Director  |  23 June 2025  |  Verified against Notes1 &amp; Notes2</t>
         </is>
       </c>
     </row>
@@ -638,7 +639,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Federal governmental actor (Department of Environment). Uses first-person 'we' for policy implementation, ministry-only questions (4.a/4.b), and describes Chief Secretary committee oversight.</t>
+          <t>Deepak Diwali, Deputy Director (Pollution Control — air and plastics), Department of Environment. Interview no. 5, 23 June 2025.</t>
         </is>
       </c>
     </row>
@@ -660,7 +661,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Public is ignorant; people know plastic is a problem but not the full extent.</t>
+          <t>Notes1 Q10: public needs awareness on health impacts; behavioural/mindset change needed. Notes2: people know but not the full extent.</t>
         </is>
       </c>
     </row>
@@ -682,7 +683,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Low political priority among decision-makers: 'no political will', plastics/waste 'not a priority' and 'stops at major' level.</t>
+          <t>Notes2: no political will; plastics/waste not a priority at decision-maker level.</t>
         </is>
       </c>
     </row>
@@ -704,7 +705,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Serious issue across rivers, lakes, land, forests; microplastics in Himalayan snow.</t>
+          <t>Notes1: problem everywhere; rivers; high leakage in water bodies; microplastics pollution.</t>
         </is>
       </c>
     </row>
@@ -726,7 +727,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Blocking sewer systems; leakage into waterways; landfill pressure.</t>
+          <t>Notes2: landfills full, blocking sewer systems. Notes1: leakage into water bodies.</t>
         </is>
       </c>
     </row>
@@ -748,7 +749,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Lots of plastics are produced.</t>
+          <t>Notes2: lots of plastics produced.</t>
         </is>
       </c>
     </row>
@@ -770,7 +771,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Inadequate waste management; limited economically viable recycling for single-use items.</t>
+          <t>Notes1: single-use plastics not economically viable to recycle; MRFs to recycling units.</t>
         </is>
       </c>
     </row>
@@ -792,7 +793,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Waste management for plastics is inadequate.</t>
+          <t>Notes1: lack of plastic waste management; high leakage in water bodies.</t>
         </is>
       </c>
     </row>
@@ -814,7 +815,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>High production rates mentioned.</t>
+          <t>Notes2: high production rates.</t>
         </is>
       </c>
     </row>
@@ -836,7 +837,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Biodegradable alternatives limited and costly (~100 NPR/kg more).</t>
+          <t>Notes1: non-availability of alternative options; biodegradable plastics costly.</t>
         </is>
       </c>
     </row>
@@ -848,7 +849,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -856,7 +857,11 @@
           <t>Lack of segregation was mentioned: yes/no</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Notes1 Q10: need for separate collection and segregation of plastics implied as gap.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Import is part of the problem space: ban on production, import, and use of bags under 40 microns explicitly targets imported plastics.</t>
+          <t>Notes1: restriction on import and use of plastic less than 40 microns in place.</t>
         </is>
       </c>
     </row>
@@ -888,7 +893,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>water, cities, biodiversity, health, agriculture</t>
+          <t>water, health</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -898,7 +903,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Water (rivers/lakes), cities (sewers/urban), biodiversity (forests), health (burning/indoor air), agriculture (research gap noted for Chitwan).</t>
+          <t>Notes1: rivers/water bodies, microplastics. Notes1 Q10: health impacts. Notes2: burning/indoor health, agriculture research gap (Chitwan).</t>
         </is>
       </c>
     </row>
@@ -956,7 +961,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Stakeholders are not collaborating or coordinating.</t>
+          <t>Notes2: stakeholders not collaborating or coordinating.</t>
         </is>
       </c>
     </row>
@@ -978,7 +983,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Challenges differ across national, district, and municipal levels; SWM Act revision needed for federal governance alignment.</t>
+          <t>Notes1 Q10: central govt policy vs LG implementation; municipals manage landfills, DoE monitors markets — multi-level split.</t>
         </is>
       </c>
     </row>
@@ -990,7 +995,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -998,7 +1003,11 @@
           <t>Unclear responsibilities among the involved actors</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Notes1 Q5: LG responsible on ground but DoE role questioned; municipals manage landfills but DoE does not monitor them.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1036,7 +1045,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Department of Environment, Chief Secretary committee, Department of Commerce and Supplies.</t>
+          <t>Department of Environment, Department of Commerce and Supplies, central government policy.</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Local governments lead waste management and collection.</t>
+          <t>Notes1: LG responsible on ground; municipals manage landfills; LG monitors markets.</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1125,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Private companies and contractors in collection/recycling.</t>
+          <t>Notes1: recycling industry; formally established industries monitored.</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1137,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1136,11 +1145,7 @@
           <t>Mentioned: yes/no</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>NGOs operate recovery facilities and awareness campaigns.</t>
-        </is>
-      </c>
+      <c r="D32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1160,7 +1165,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Cites studies on microplastics; notes limited research on health/environmental effects.</t>
+          <t>Notes2: not much research on effects of plastics; more research needed.</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1187,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Household waste reduction discussed; 300 NPR/month collector incentive mentioned (household incentive, not a product tax).</t>
+          <t>Notes1 Q9–10: waste producers; implementation at household level; Notes2: 300 NPR household incentive.</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1202,7 +1207,11 @@
           <t>Mentioned: yes/no</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Notes1 Q10: schools mentioned for implementation; kids already taught about plastics.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1222,7 +1231,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Private contractors, plastic producers, and markets monitored by Department of Environment.</t>
+          <t>Notes1: plastic producers monitored; informal industries harder to surveil.</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1271,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Implementation is always the problem; monitoring cited as barrier.</t>
+          <t>Notes1: lack of surveillance; monitors only 2–3 times/year; too few staff. Notes2: implementation/monitoring is the problem.</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1293,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Funds exist but are not released; earmarked funds may be frozen if unused.</t>
+          <t>Notes2: funds exist but not released; earmarked funds frozen if unused. Notes1: grant/subsidy provisions being developed for industry shift.</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1315,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Limited knowledge and research on health/environmental effects.</t>
+          <t>Notes2: not much research/knowledge on plastic effects.</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1337,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Facilities exist in at least some contexts ('facility is there'); not coded as a primary lack-of-infrastructure barrier.</t>
+          <t>Notes2: facilities exist in some contexts. Notes1: MRFs in use — not coded as primary infrastructure gap.</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1359,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Weak enforcement; cheaper plastics remain in use despite bans.</t>
+          <t>Notes1: no penalty in place; lack of surveillance. Notes1/2: weak enforcement.</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1417,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Ban on production, import, and use of plastic bags under 40 microns.</t>
+          <t>Notes1: restriction on import and use of plastic &lt;40 microns.</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1439,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Government documentaries, traditional/social media, website materials.</t>
+          <t>Notes1 Q10: awareness campaigns and advocacy through documentaries.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1451,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1450,7 +1459,11 @@
           <t>Education programs</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Notes1 Q10: education in schools; kids taught about plastics.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -1506,7 +1519,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>No levy/tax on specific products coded. The 300 NPR/month measure is a household waste-reduction incentive for collectors, not a bag tax/levy.</t>
+          <t>No product levy/tax coded. Notes1: planned grant/subsidy for industry shift (financial incentive, not a bag tax).</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1541,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Ban on bags under 40 microns and plastic decorative flowers.</t>
+          <t>Notes1: ban on plastic flowers and bags (&lt;40 microns).</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1563,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Biodegradable starch bags discussed as existing but costly alternative.</t>
+          <t>Notes1: biodegradable plastics produced; govt exploring subsidies for environment-friendly alternatives.</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1621,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Material recovery facilities send recyclables to processing units.</t>
+          <t>Notes1: MRFs and recycling units; circular economy discussed.</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1643,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Collection by local governments or private contractors.</t>
+          <t>Notes1 Q10: collection system with separate collection needed/implied as measure.</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1683,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>High-level committee chaired by Chief Secretary oversees measures.</t>
+          <t>Notes1: need for a specific plastics management guideline (national framework).</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1705,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>EPR framed as key missing responsibility mechanism.</t>
+          <t>Notes1: EPR / polluters-pay principle; clarify DoE monitoring role.</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1727,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>EPR identified as key gap; no producer responsibility in Nepal.</t>
+          <t>Notes1: no EPR in Nepal; polluters-pay principle recommended.</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1749,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Need for communication and awareness on how to act.</t>
+          <t>Notes1 Q10: awareness on health impacts; behavioural/mindset change needed.</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1761,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -1758,7 +1771,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Collection/recycling encouraged, but segregation not proposed as a forward solution.</t>
+          <t>Notes1 Theme D &amp; Q10: segregation of plastics; separate collection; systematic circulation/circular economy.</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1809,11 @@
           <t>New raw materials</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Notes1: circular economy; MRFs to recycling units.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -1814,7 +1831,11 @@
           <t>Education programs at schools</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Notes1 Q9–10: education for plastic producers; schools; public learning on health impacts.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -1824,7 +1845,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -1832,7 +1853,11 @@
           <t>Capacity-building programs</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Notes1: inadequate monitoring due to too few staff (only 2–3 inspections/year).</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -1852,7 +1877,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D needed for affordable alternatives.</t>
+          <t>Notes2: R&amp;D for alternatives needed. Notes1: need environment-friendly plastics.</t>
         </is>
       </c>
     </row>
@@ -1890,11 +1915,7 @@
           <t>Ban of products</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>Bans described as existing policy; forward-looking solutions emphasize EPR, R&amp;D, communication, and mitigation/adaptation rather than new bans.</t>
-        </is>
-      </c>
+      <c r="D69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -1914,7 +1935,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Financial support identified in Q10.</t>
+          <t>Notes1: incentives for alternatives; planned grants to shift industry from 40-micron plastics.</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1957,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Infrastructural support identified in Q10.</t>
+          <t>Notes1 Q10: collection system, separate collection, biodegradable waste to manure.</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1979,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Affordable eco-friendly substitutes needed before behaviour change.</t>
+          <t>Notes1: need affordable eco-friendly alternatives; subsidy for biodegradable products.</t>
         </is>
       </c>
     </row>
@@ -1998,7 +2019,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Enforcement procedures needed alongside bans.</t>
+          <t>Notes1: no penalty in place; need stronger enforcement.</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2041,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Monitoring improvements implied from implementation challenges.</t>
+          <t>Notes1: strengthen DoE monitoring; increase frequency beyond 2–3 times/year.</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2063,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Follow-up asked (Q8) but no specific tradition recorded.</t>
+          <t>Notes2 follow-up asked; Notes1 cites Bhaktapur as example only — no tradition coded.</t>
         </is>
       </c>
     </row>
@@ -2568,234 +2589,234 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>water, health</t>
+        </is>
+      </c>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="P2" s="7" t="inlineStr">
-        <is>
-          <t>water, cities, biodiversity, health, agriculture</t>
-        </is>
-      </c>
-      <c r="Q2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="X2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="T2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="Y2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Z2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="V2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="W2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="X2" s="7" t="inlineStr">
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="Y2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="Z2" s="7" t="inlineStr">
+      <c r="AC2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AE2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AF2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AH2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AJ2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AK2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AA2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AC2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AE2" s="7" t="inlineStr">
+      <c r="AL2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AM2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AF2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AG2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AH2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AI2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AJ2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AK2" s="7" t="inlineStr">
+      <c r="AO2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AP2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AQ2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AL2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AM2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AN2" s="7" t="inlineStr">
+      <c r="AS2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AO2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AP2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AQ2" s="7" t="inlineStr">
+      <c r="AT2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AR2" s="7" t="inlineStr">
+      <c r="AU2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AV2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AW2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AS2" s="7" t="inlineStr">
+      <c r="AX2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AT2" s="7" t="inlineStr">
+      <c r="AY2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG2" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AU2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AV2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AW2" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AX2" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AY2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AZ2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BA2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BB2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BC2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BD2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BE2" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BF2" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="BG2" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="BH2" s="7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2808,7 +2829,7 @@
       </c>
       <c r="BJ2" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="BK2" s="7" t="inlineStr">
@@ -3765,7 +3786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3806,72 +3827,172 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Coded actor type</t>
+          <t>Interview number</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>governmental</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Likely affiliation</t>
+          <t>Interview date</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Department of Environment / Ministry of Forests and Environment (federal)</t>
+          <t>23 June 2025 (3:50pm – 4:40pm)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Role in plastic governance</t>
+          <t>Affiliation</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>National policy design, monitoring of producers/markets, awareness campaigns, SWM Act revision</t>
+          <t>Department of Environment, Ministry of Forests and Environment</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Perspective</t>
+          <t>Interviewee</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Insider — describes measures as 'we' (government actor implementing national plastic policy)</t>
+          <t>Deepak Diwali — Deputy Director, Pollution Control (air and plastics)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Coded actor type</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>High for governmental coding; see RSCT note below</t>
+          <t>governmental</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>RSCT note</t>
+          <t>Role in plastic governance</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Page 1 contains RSCT cooperative profile notes (est. 1991, 200+ cooperatives, grassroots loans, recently urban plastics). This does not match the interview voice in Themes A–D, which is clearly a federal ministry/department official. RSCT notes are treated as misplaced interviewer notes, not the coded stakeholder.</t>
+          <t>Federal monitoring of plastic producers/markets; policy instruments (import restrictions, bans); SWM Act revision; coordination with local governments and Department of Commerce and Supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Perspective</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Insider — describes DoE monitoring role, planned grants, and national policy instruments</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Verification status</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Confirmed Environmental Department / Ministry interview</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Source documents</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Notes1 (primary), Notes2 (supplementary)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Source Documents Used for Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Notes1 — Department of Environment (primary)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Interview no. 5, 23 June 2025, 3:50–4:40pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Notes2 — Department of Environment (supplementary)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Interview guideline with interviewer bullet notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Codebook</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Overview All Interviews — NEW Codebook</t>
         </is>
       </c>
     </row>
